--- a/assets/constructions/examples/ctd_ethd_straight.xlsx
+++ b/assets/constructions/examples/ctd_ethd_straight.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AE5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,6 +564,26 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -651,31 +671,29 @@
           <t>2021/ http://www.tool-cloud.de/zh/online-catalogue</t>
         </is>
       </c>
+      <c r="AB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>01.130.125.103</t>
+          <t>40.3025TOEM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WERDEN</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>DIN 5482</t>
-        </is>
-      </c>
+          <t>EWS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DIN_69880:DIN_5482:30</t>
+          <t>DIN_69880:TOEM:30</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -688,12 +706,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ER25</t>
+          <t>EWS_ER-25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ISO</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -702,67 +720,73 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>42</v>
       </c>
       <c r="M3" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N3" t="n">
         <v>30</v>
       </c>
       <c r="O3" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P3" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>70</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
         <v>62</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="n">
-        <v>6000</v>
-      </c>
-      <c r="Y3" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020 / WERDEN Catalog</t>
-        </is>
-      </c>
+          <t>2021/ http://www.tool-cloud.de/zh/online-catalogue</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>40.3025TOEM</t>
+          <t>DS30DTAER25AR2712622</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DIN_69880:TOEM:30</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -775,12 +799,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>EWS_ER-25</t>
+          <t>WID_ER-25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -789,33 +813,21 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>42</v>
-      </c>
-      <c r="M4" t="n">
-        <v>70</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
         <v>30</v>
       </c>
-      <c r="O4" t="n">
-        <v>89</v>
-      </c>
-      <c r="P4" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>70</v>
-      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>62</v>
-      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -830,26 +842,40 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021/ http://www.tool-cloud.de/zh/online-catalogue</t>
-        </is>
-      </c>
+          <t>2021/https://www.machiningcloud.com/</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DS30DTAER25AR2712622</t>
+          <t>01.130.125.103</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WIDIA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>WERDEN</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DIN 5482</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>DIN_69880:DIN_5482:30</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -862,12 +888,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>WID_ER-25</t>
+          <t>ER25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>ISO</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -878,36 +904,54 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>42</v>
+      </c>
+      <c r="M5" t="n">
+        <v>68</v>
+      </c>
       <c r="N5" t="n">
         <v>30</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>90</v>
+      </c>
+      <c r="P5" t="n">
+        <v>62</v>
+      </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="b">
         <v>0</v>
       </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>6000</v>
+      </c>
+      <c r="Y5" t="b">
+        <v>0</v>
+      </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021/https://www.machiningcloud.com/</t>
-        </is>
-      </c>
+          <t>2020 / WERDEN Catalog</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
